--- a/entertainment_forms/022_match_maker_form--entertainment_forms.xlsx
+++ b/entertainment_forms/022_match_maker_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Male', 'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Female', 'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Never', 'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single',_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Single', 'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_a_relationship',_'value':_'in_a_relationship'}</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In a Relationship', 'value': 'In a Relationship'}</t>
+          <t>In a Relationship</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'married',_'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Married', 'value': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
